--- a/interestelar_300.xlsx
+++ b/interestelar_300.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebasaluuclm-my.sharepoint.com/personal/miguelangel_tarancon_uclm_es/Documents/Documentos/curso/Cursos de Datos/New Book/RStars-book/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="11_B67AFED58D1128E4B8170BFD139FF01550298D8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A17DB47E-5D49-4FC1-8681-E07D49F39A77}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_B67AFED58D1128E4B8170BFD139FF01550298D8C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7DA4DAF3-391E-4F04-978E-15F175CC24C0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Datos!$A$1:$AC$301</definedName>
   </definedNames>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1467,16 +1480,16 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
+        <top style="thin">
           <color auto="1"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
+        <bottom style="thin">
           <color auto="1"/>
-        </top>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -1597,7 +1610,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B470C0D-608A-48EB-B129-16744DB71A76}" name="Tabla2" displayName="Tabla2" ref="A1:C27" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="1" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B470C0D-608A-48EB-B129-16744DB71A76}" name="Tabla2" displayName="Tabla2" ref="A1:C27" totalsRowShown="0" headerRowDxfId="3" headerRowBorderDxfId="2" tableBorderDxfId="1">
   <autoFilter ref="A1:C27" xr:uid="{1B470C0D-608A-48EB-B129-16744DB71A76}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{F648B1CA-E561-49C7-9948-BA710C82DDAD}" name="Variable" dataDxfId="0"/>
@@ -1896,28 +1909,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CC5D604-15B4-41A1-A12D-AE079EBAF1B2}">
   <dimension ref="B1:B28"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="10.28515625" style="1"/>
+    <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="10.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:2" ht="25.8" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B28" s="2" t="s">
         <v>373</v>
       </c>
@@ -1931,14 +1944,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8622719-6107-4359-B2C8-94B2028CC0A5}">
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" customWidth="1"/>
-    <col min="2" max="2" width="73.140625" customWidth="1"/>
-    <col min="3" max="3" width="48.7109375" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" customWidth="1"/>
+    <col min="2" max="2" width="73.109375" customWidth="1"/>
+    <col min="3" max="3" width="48.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>374</v>
       </c>
@@ -1949,7 +1962,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>3</v>
       </c>
@@ -1960,7 +1973,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
@@ -1971,7 +1984,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -1982,7 +1995,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -1993,7 +2006,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -2004,7 +2017,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -2015,7 +2028,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
@@ -2026,7 +2039,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>10</v>
       </c>
@@ -2037,7 +2050,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
@@ -2048,7 +2061,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
@@ -2059,7 +2072,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
@@ -2070,7 +2083,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>14</v>
       </c>
@@ -2081,7 +2094,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
@@ -2092,7 +2105,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
@@ -2103,7 +2116,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
@@ -2114,7 +2127,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>18</v>
       </c>
@@ -2125,7 +2138,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
@@ -2136,7 +2149,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>20</v>
       </c>
@@ -2147,7 +2160,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
@@ -2158,7 +2171,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>22</v>
       </c>
@@ -2169,7 +2182,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
@@ -2180,7 +2193,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>24</v>
       </c>
@@ -2191,7 +2204,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>25</v>
       </c>
@@ -2202,7 +2215,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>26</v>
       </c>
@@ -2213,7 +2226,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>27</v>
       </c>
@@ -2224,7 +2237,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>28</v>
       </c>
@@ -2246,41 +2259,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC301"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.28515625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.5703125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="13.7109375" style="6" customWidth="1"/>
-    <col min="10" max="10" width="10.5703125" style="6" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" style="6" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5703125" style="6" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" style="6" customWidth="1"/>
-    <col min="18" max="18" width="7.5703125" style="6" customWidth="1"/>
+    <col min="1" max="1" width="30.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="6" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.6640625" style="6" customWidth="1"/>
+    <col min="10" max="10" width="10.5546875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.5546875" style="6" customWidth="1"/>
+    <col min="16" max="16" width="9.109375" style="6" customWidth="1"/>
+    <col min="17" max="17" width="6.44140625" style="6" customWidth="1"/>
+    <col min="18" max="18" width="7.5546875" style="6" customWidth="1"/>
     <col min="19" max="19" width="11" style="6" customWidth="1"/>
-    <col min="20" max="20" width="10.140625" style="6" customWidth="1"/>
-    <col min="21" max="21" width="9.140625" style="6" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="6" customWidth="1"/>
-    <col min="23" max="23" width="10.140625" style="6" customWidth="1"/>
+    <col min="20" max="20" width="10.109375" style="6" customWidth="1"/>
+    <col min="21" max="21" width="9.109375" style="6" customWidth="1"/>
+    <col min="22" max="22" width="14.5546875" style="6" customWidth="1"/>
+    <col min="23" max="23" width="10.109375" style="6" customWidth="1"/>
     <col min="24" max="24" width="8" style="6" customWidth="1"/>
-    <col min="25" max="25" width="9.42578125" style="6" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.5703125" style="6" customWidth="1"/>
-    <col min="27" max="27" width="11.140625" style="6" customWidth="1"/>
-    <col min="28" max="28" width="9.140625" style="6" customWidth="1"/>
-    <col min="29" max="29" width="10.7109375" style="6" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="10.28515625" style="6"/>
+    <col min="25" max="25" width="9.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.5546875" style="6" customWidth="1"/>
+    <col min="27" max="27" width="11.109375" style="6" customWidth="1"/>
+    <col min="28" max="28" width="9.109375" style="6" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="10.33203125" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -2369,7 +2382,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>34</v>
       </c>
@@ -2458,7 +2471,7 @@
         <v>1871.7084025189299</v>
       </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>79</v>
       </c>
@@ -2547,7 +2560,7 @@
         <v>1518.799186600321</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>316</v>
       </c>
@@ -2636,7 +2649,7 @@
         <v>5895.2033004042933</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>41</v>
       </c>
@@ -2725,7 +2738,7 @@
         <v>2900.0209563221788</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>124</v>
       </c>
@@ -2814,7 +2827,7 @@
         <v>1137.0186814254851</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>99</v>
       </c>
@@ -2903,7 +2916,7 @@
         <v>5940.4747198483774</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>173</v>
       </c>
@@ -2992,7 +3005,7 @@
         <v>862.1593791078252</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>314</v>
       </c>
@@ -3081,7 +3094,7 @@
         <v>14936.4146993062</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>232</v>
       </c>
@@ -3170,7 +3183,7 @@
         <v>3469.0374105855381</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>60</v>
       </c>
@@ -3259,7 +3272,7 @@
         <v>6133.144077148977</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>171</v>
       </c>
@@ -3348,7 +3361,7 @@
         <v>4584.5855049498005</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>242</v>
       </c>
@@ -3437,7 +3450,7 @@
         <v>2172.364679502522</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>134</v>
       </c>
@@ -3526,7 +3539,7 @@
         <v>2095.3104387334538</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>200</v>
       </c>
@@ -3615,7 +3628,7 @@
         <v>234.86236750854269</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>130</v>
       </c>
@@ -3704,7 +3717,7 @@
         <v>4621.8269392085731</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>138</v>
       </c>
@@ -3793,7 +3806,7 @@
         <v>1184.0038201806551</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>160</v>
       </c>
@@ -3882,7 +3895,7 @@
         <v>1341.078463219369</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>86</v>
       </c>
@@ -3971,7 +3984,7 @@
         <v>4063.28285718489</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>85</v>
       </c>
@@ -4060,7 +4073,7 @@
         <v>3896.6674197921379</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>106</v>
       </c>
@@ -4149,7 +4162,7 @@
         <v>7226.7456680565583</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>38</v>
       </c>
@@ -4238,7 +4251,7 @@
         <v>1130.1208127499769</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>63</v>
       </c>
@@ -4327,7 +4340,7 @@
         <v>2444.7842081042081</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>52</v>
       </c>
@@ -4416,7 +4429,7 @@
         <v>768.10875188717955</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>31</v>
       </c>
@@ -4505,7 +4518,7 @@
         <v>1716.498935032394</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>164</v>
       </c>
@@ -4594,7 +4607,7 @@
         <v>30729.908437887902</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>165</v>
       </c>
@@ -4683,7 +4696,7 @@
         <v>2187.9785929615232</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>75</v>
       </c>
@@ -4772,7 +4785,7 @@
         <v>76097.339504029704</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>157</v>
       </c>
@@ -4861,7 +4874,7 @@
         <v>990.03662319482112</v>
       </c>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>236</v>
       </c>
@@ -4950,7 +4963,7 @@
         <v>1187.129077090638</v>
       </c>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>76</v>
       </c>
@@ -5039,7 +5052,7 @@
         <v>29545.011740892471</v>
       </c>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>276</v>
       </c>
@@ -5128,7 +5141,7 @@
         <v>990.65162327044891</v>
       </c>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>261</v>
       </c>
@@ -5217,7 +5230,7 @@
         <v>6133.3062167059952</v>
       </c>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>241</v>
       </c>
@@ -5306,7 +5319,7 @@
         <v>1621.0376821750051</v>
       </c>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>291</v>
       </c>
@@ -5395,7 +5408,7 @@
         <v>235.10137629384579</v>
       </c>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>267</v>
       </c>
@@ -5484,7 +5497,7 @@
         <v>7487.423385289977</v>
       </c>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>324</v>
       </c>
@@ -5573,7 +5586,7 @@
         <v>79.316176170079871</v>
       </c>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>188</v>
       </c>
@@ -5662,7 +5675,7 @@
         <v>24466.243894815609</v>
       </c>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>304</v>
       </c>
@@ -5751,7 +5764,7 @@
         <v>10490.963486926241</v>
       </c>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>42</v>
       </c>
@@ -5840,7 +5853,7 @@
         <v>8214.4592563649367</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>250</v>
       </c>
@@ -5929,7 +5942,7 @@
         <v>1693.550175821995</v>
       </c>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>301</v>
       </c>
@@ -6018,7 +6031,7 @@
         <v>178.5970377540666</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>102</v>
       </c>
@@ -6107,7 +6120,7 @@
         <v>216.47044786596669</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>44</v>
       </c>
@@ -6196,7 +6209,7 @@
         <v>498.86676343052369</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>262</v>
       </c>
@@ -6285,7 +6298,7 @@
         <v>1628.0130267574671</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>303</v>
       </c>
@@ -6374,7 +6387,7 @@
         <v>22060.984535758998</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>253</v>
       </c>
@@ -6463,7 +6476,7 @@
         <v>1991.04754519529</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>308</v>
       </c>
@@ -6552,7 +6565,7 @@
         <v>6162.645077882753</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>53</v>
       </c>
@@ -6641,7 +6654,7 @@
         <v>2358.3868404233021</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>298</v>
       </c>
@@ -6730,7 +6743,7 @@
         <v>5216.3937283753612</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>238</v>
       </c>
@@ -6819,7 +6832,7 @@
         <v>1394.1325081311779</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>176</v>
       </c>
@@ -6908,7 +6921,7 @@
         <v>7451.9554031765574</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>148</v>
       </c>
@@ -6997,7 +7010,7 @@
         <v>4001.4271534741329</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>88</v>
       </c>
@@ -7086,7 +7099,7 @@
         <v>9855.3180369739966</v>
       </c>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>174</v>
       </c>
@@ -7175,7 +7188,7 @@
         <v>2438.1133684912852</v>
       </c>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>137</v>
       </c>
@@ -7264,7 +7277,7 @@
         <v>39288.85185020254</v>
       </c>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>73</v>
       </c>
@@ -7353,7 +7366,7 @@
         <v>2936.6856338150801</v>
       </c>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>154</v>
       </c>
@@ -7442,7 +7455,7 @@
         <v>3803.1594487878069</v>
       </c>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>72</v>
       </c>
@@ -7531,7 +7544,7 @@
         <v>2874.153472449867</v>
       </c>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>197</v>
       </c>
@@ -7620,7 +7633,7 @@
         <v>2164.7334365718571</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>249</v>
       </c>
@@ -7709,7 +7722,7 @@
         <v>6290.5745722370248</v>
       </c>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>215</v>
       </c>
@@ -7798,7 +7811,7 @@
         <v>935.82609615118088</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>258</v>
       </c>
@@ -7887,7 +7900,7 @@
         <v>959.70107969721448</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>326</v>
       </c>
@@ -7976,7 +7989,7 @@
         <v>716.03855236487607</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>49</v>
       </c>
@@ -8065,7 +8078,7 @@
         <v>3308.4289690579981</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>133</v>
       </c>
@@ -8154,7 +8167,7 @@
         <v>635.0818168151086</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>190</v>
       </c>
@@ -8243,7 +8256,7 @@
         <v>1156.181845705981</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>307</v>
       </c>
@@ -8332,7 +8345,7 @@
         <v>531.79938455272156</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>193</v>
       </c>
@@ -8421,7 +8434,7 @@
         <v>530.37444873533695</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>206</v>
       </c>
@@ -8510,7 +8523,7 @@
         <v>402.13561125599011</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>129</v>
       </c>
@@ -8599,7 +8612,7 @@
         <v>675.45233707488683</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>78</v>
       </c>
@@ -8688,7 +8701,7 @@
         <v>171.98182493435459</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>177</v>
       </c>
@@ -8777,7 +8790,7 @@
         <v>2198.6728635483091</v>
       </c>
     </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>97</v>
       </c>
@@ -8866,7 +8879,7 @@
         <v>4862.2642083098499</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>186</v>
       </c>
@@ -8955,7 +8968,7 @@
         <v>2843.9893276095931</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>210</v>
       </c>
@@ -9044,7 +9057,7 @@
         <v>193.27869146955899</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>189</v>
       </c>
@@ -9133,7 +9146,7 @@
         <v>2736.2851580961601</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>56</v>
       </c>
@@ -9222,7 +9235,7 @@
         <v>2659.1488900986928</v>
       </c>
     </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>295</v>
       </c>
@@ -9311,7 +9324,7 @@
         <v>616.39734134391574</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>279</v>
       </c>
@@ -9400,7 +9413,7 @@
         <v>159.36084637744489</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>293</v>
       </c>
@@ -9489,7 +9502,7 @@
         <v>7166.8729380663217</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>168</v>
       </c>
@@ -9578,7 +9591,7 @@
         <v>259.23004264691679</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>325</v>
       </c>
@@ -9667,7 +9680,7 @@
         <v>205.57143037256509</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>281</v>
       </c>
@@ -9756,7 +9769,7 @@
         <v>616.83271140078784</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>183</v>
       </c>
@@ -9845,7 +9858,7 @@
         <v>262555.81510226981</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>195</v>
       </c>
@@ -9934,7 +9947,7 @@
         <v>191.78319008507441</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>68</v>
       </c>
@@ -10023,7 +10036,7 @@
         <v>1944.401284920679</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>194</v>
       </c>
@@ -10112,7 +10125,7 @@
         <v>344.12221804261378</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>108</v>
       </c>
@@ -10201,7 +10214,7 @@
         <v>1032.6610772929239</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>144</v>
       </c>
@@ -10290,7 +10303,7 @@
         <v>688.94456074239019</v>
       </c>
     </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>122</v>
       </c>
@@ -10379,7 +10392,7 @@
         <v>4907.0954588428876</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>319</v>
       </c>
@@ -10468,7 +10481,7 @@
         <v>201.17565879121119</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>87</v>
       </c>
@@ -10557,7 +10570,7 @@
         <v>10414.726861145509</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>321</v>
       </c>
@@ -10646,7 +10659,7 @@
         <v>4387.1864282829374</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>83</v>
       </c>
@@ -10735,7 +10748,7 @@
         <v>262.5043795892505</v>
       </c>
     </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>268</v>
       </c>
@@ -10824,7 +10837,7 @@
         <v>377.87861520714898</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>125</v>
       </c>
@@ -10913,7 +10926,7 @@
         <v>2445.4788837375659</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>127</v>
       </c>
@@ -11002,7 +11015,7 @@
         <v>2796.8214863505618</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>146</v>
       </c>
@@ -11091,7 +11104,7 @@
         <v>1191.7204600677289</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>98</v>
       </c>
@@ -11180,7 +11193,7 @@
         <v>4669.3599193599193</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>182</v>
       </c>
@@ -11269,7 +11282,7 @@
         <v>26757.253390952461</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>112</v>
       </c>
@@ -11358,7 +11371,7 @@
         <v>265.33840905863912</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>230</v>
       </c>
@@ -11447,7 +11460,7 @@
         <v>2862.3115421968619</v>
       </c>
     </row>
-    <row r="104" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>114</v>
       </c>
@@ -11536,7 +11549,7 @@
         <v>187.33827230767679</v>
       </c>
     </row>
-    <row r="105" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>263</v>
       </c>
@@ -11625,7 +11638,7 @@
         <v>3136.0013462543079</v>
       </c>
     </row>
-    <row r="106" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>62</v>
       </c>
@@ -11714,7 +11727,7 @@
         <v>466.54170214862381</v>
       </c>
     </row>
-    <row r="107" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>257</v>
       </c>
@@ -11803,7 +11816,7 @@
         <v>11512.413385141799</v>
       </c>
     </row>
-    <row r="108" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>248</v>
       </c>
@@ -11892,7 +11905,7 @@
         <v>1153.278981452027</v>
       </c>
     </row>
-    <row r="109" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>191</v>
       </c>
@@ -11981,7 +11994,7 @@
         <v>69882.52092919228</v>
       </c>
     </row>
-    <row r="110" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>312</v>
       </c>
@@ -12070,7 +12083,7 @@
         <v>738.00022996465452</v>
       </c>
     </row>
-    <row r="111" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>255</v>
       </c>
@@ -12159,7 +12172,7 @@
         <v>2382.6032065734389</v>
       </c>
     </row>
-    <row r="112" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>61</v>
       </c>
@@ -12248,7 +12261,7 @@
         <v>7620.0120881725516</v>
       </c>
     </row>
-    <row r="113" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>246</v>
       </c>
@@ -12337,7 +12350,7 @@
         <v>995.59306737156385</v>
       </c>
     </row>
-    <row r="114" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>260</v>
       </c>
@@ -12426,7 +12439,7 @@
         <v>614.24123833598594</v>
       </c>
     </row>
-    <row r="115" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>54</v>
       </c>
@@ -12515,7 +12528,7 @@
         <v>4247.0290739679613</v>
       </c>
     </row>
-    <row r="116" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>212</v>
       </c>
@@ -12604,7 +12617,7 @@
         <v>17384.12185417036</v>
       </c>
     </row>
-    <row r="117" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>282</v>
       </c>
@@ -12693,7 +12706,7 @@
         <v>16153.048935592889</v>
       </c>
     </row>
-    <row r="118" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>45</v>
       </c>
@@ -12782,7 +12795,7 @@
         <v>2715.3470754820519</v>
       </c>
     </row>
-    <row r="119" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>81</v>
       </c>
@@ -12871,7 +12884,7 @@
         <v>929.84720876274946</v>
       </c>
     </row>
-    <row r="120" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>271</v>
       </c>
@@ -12960,7 +12973,7 @@
         <v>2512.1523851508509</v>
       </c>
     </row>
-    <row r="121" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>92</v>
       </c>
@@ -13049,7 +13062,7 @@
         <v>660.35488817149792</v>
       </c>
     </row>
-    <row r="122" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>302</v>
       </c>
@@ -13138,7 +13151,7 @@
         <v>334.52534418113589</v>
       </c>
     </row>
-    <row r="123" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>322</v>
       </c>
@@ -13227,7 +13240,7 @@
         <v>434.34833303982401</v>
       </c>
     </row>
-    <row r="124" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>285</v>
       </c>
@@ -13316,7 +13329,7 @@
         <v>292.88969583372977</v>
       </c>
     </row>
-    <row r="125" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>77</v>
       </c>
@@ -13405,7 +13418,7 @@
         <v>214.01052814145021</v>
       </c>
     </row>
-    <row r="126" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>145</v>
       </c>
@@ -13494,7 +13507,7 @@
         <v>6173.1837808115952</v>
       </c>
     </row>
-    <row r="127" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>159</v>
       </c>
@@ -13583,7 +13596,7 @@
         <v>266.88228149731577</v>
       </c>
     </row>
-    <row r="128" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>220</v>
       </c>
@@ -13672,7 +13685,7 @@
         <v>1426.098621219119</v>
       </c>
     </row>
-    <row r="129" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>272</v>
       </c>
@@ -13761,7 +13774,7 @@
         <v>126.61628538763679</v>
       </c>
     </row>
-    <row r="130" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>231</v>
       </c>
@@ -13850,7 +13863,7 @@
         <v>65801.149425287251</v>
       </c>
     </row>
-    <row r="131" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>100</v>
       </c>
@@ -13939,7 +13952,7 @@
         <v>277.20284647754562</v>
       </c>
     </row>
-    <row r="132" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>95</v>
       </c>
@@ -14028,7 +14041,7 @@
         <v>14248.32678711703</v>
       </c>
     </row>
-    <row r="133" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>50</v>
       </c>
@@ -14117,7 +14130,7 @@
         <v>291.66722499730292</v>
       </c>
     </row>
-    <row r="134" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>185</v>
       </c>
@@ -14206,7 +14219,7 @@
         <v>988.34584784559354</v>
       </c>
     </row>
-    <row r="135" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>155</v>
       </c>
@@ -14295,7 +14308,7 @@
         <v>2175.1416538924332</v>
       </c>
     </row>
-    <row r="136" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>105</v>
       </c>
@@ -14384,7 +14397,7 @@
         <v>22230.21221146686</v>
       </c>
     </row>
-    <row r="137" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>274</v>
       </c>
@@ -14473,7 +14486,7 @@
         <v>8227.4294685111036</v>
       </c>
     </row>
-    <row r="138" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>139</v>
       </c>
@@ -14562,7 +14575,7 @@
         <v>185.45781963666329</v>
       </c>
     </row>
-    <row r="139" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>57</v>
       </c>
@@ -14651,7 +14664,7 @@
         <v>410.79560687180071</v>
       </c>
     </row>
-    <row r="140" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>243</v>
       </c>
@@ -14740,7 +14753,7 @@
         <v>4062.837751407088</v>
       </c>
     </row>
-    <row r="141" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>198</v>
       </c>
@@ -14829,7 +14842,7 @@
         <v>1024.9005424168399</v>
       </c>
     </row>
-    <row r="142" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>111</v>
       </c>
@@ -14918,7 +14931,7 @@
         <v>5555.4556080349194</v>
       </c>
     </row>
-    <row r="143" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>202</v>
       </c>
@@ -15007,7 +15020,7 @@
         <v>5146.7134892477006</v>
       </c>
     </row>
-    <row r="144" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>30</v>
       </c>
@@ -15096,7 +15109,7 @@
         <v>659.86751499693639</v>
       </c>
     </row>
-    <row r="145" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>104</v>
       </c>
@@ -15185,7 +15198,7 @@
         <v>7814.4472115391336</v>
       </c>
     </row>
-    <row r="146" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>240</v>
       </c>
@@ -15274,7 +15287,7 @@
         <v>417.8220069557658</v>
       </c>
     </row>
-    <row r="147" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>278</v>
       </c>
@@ -15363,7 +15376,7 @@
         <v>1300.07541738346</v>
       </c>
     </row>
-    <row r="148" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>110</v>
       </c>
@@ -15452,7 +15465,7 @@
         <v>386.96851110048698</v>
       </c>
     </row>
-    <row r="149" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>131</v>
       </c>
@@ -15541,7 +15554,7 @@
         <v>694.92278625339441</v>
       </c>
     </row>
-    <row r="150" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>217</v>
       </c>
@@ -15630,7 +15643,7 @@
         <v>1689.430498009586</v>
       </c>
     </row>
-    <row r="151" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>136</v>
       </c>
@@ -15719,7 +15732,7 @@
         <v>932.00210748155939</v>
       </c>
     </row>
-    <row r="152" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>251</v>
       </c>
@@ -15808,7 +15821,7 @@
         <v>177.44956294423301</v>
       </c>
     </row>
-    <row r="153" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>90</v>
       </c>
@@ -15897,7 +15910,7 @@
         <v>25900.913636093079</v>
       </c>
     </row>
-    <row r="154" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>65</v>
       </c>
@@ -15986,7 +15999,7 @@
         <v>2746.8478277518811</v>
       </c>
     </row>
-    <row r="155" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>235</v>
       </c>
@@ -16075,7 +16088,7 @@
         <v>1232.7462051375401</v>
       </c>
     </row>
-    <row r="156" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>39</v>
       </c>
@@ -16164,7 +16177,7 @@
         <v>2659.169612363678</v>
       </c>
     </row>
-    <row r="157" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>142</v>
       </c>
@@ -16253,7 +16266,7 @@
         <v>211927.91005291001</v>
       </c>
     </row>
-    <row r="158" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>140</v>
       </c>
@@ -16342,7 +16355,7 @@
         <v>185.96230483438481</v>
       </c>
     </row>
-    <row r="159" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>93</v>
       </c>
@@ -16431,7 +16444,7 @@
         <v>9873.1068473016567</v>
       </c>
     </row>
-    <row r="160" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>128</v>
       </c>
@@ -16520,7 +16533,7 @@
         <v>370.91914079511821</v>
       </c>
     </row>
-    <row r="161" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>152</v>
       </c>
@@ -16609,7 +16622,7 @@
         <v>962.35562116560652</v>
       </c>
     </row>
-    <row r="162" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>107</v>
       </c>
@@ -16698,7 +16711,7 @@
         <v>8517.4405961679204</v>
       </c>
     </row>
-    <row r="163" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A163" s="6" t="s">
         <v>296</v>
       </c>
@@ -16787,7 +16800,7 @@
         <v>5549.1373568528034</v>
       </c>
     </row>
-    <row r="164" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A164" s="6" t="s">
         <v>33</v>
       </c>
@@ -16876,7 +16889,7 @@
         <v>211.45470910054249</v>
       </c>
     </row>
-    <row r="165" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A165" s="6" t="s">
         <v>43</v>
       </c>
@@ -16965,7 +16978,7 @@
         <v>2350.8793696857542</v>
       </c>
     </row>
-    <row r="166" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A166" s="6" t="s">
         <v>172</v>
       </c>
@@ -17054,7 +17067,7 @@
         <v>1310.3274163880869</v>
       </c>
     </row>
-    <row r="167" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A167" s="6" t="s">
         <v>135</v>
       </c>
@@ -17143,7 +17156,7 @@
         <v>773.56181563053394</v>
       </c>
     </row>
-    <row r="168" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A168" s="6" t="s">
         <v>162</v>
       </c>
@@ -17232,7 +17245,7 @@
         <v>1514.4522142346759</v>
       </c>
     </row>
-    <row r="169" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A169" s="6" t="s">
         <v>256</v>
       </c>
@@ -17321,7 +17334,7 @@
         <v>9209.8214285714294</v>
       </c>
     </row>
-    <row r="170" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A170" s="6" t="s">
         <v>115</v>
       </c>
@@ -17410,7 +17423,7 @@
         <v>715.26482231775583</v>
       </c>
     </row>
-    <row r="171" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A171" s="6" t="s">
         <v>201</v>
       </c>
@@ -17499,7 +17512,7 @@
         <v>349.44971382615512</v>
       </c>
     </row>
-    <row r="172" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A172" s="6" t="s">
         <v>290</v>
       </c>
@@ -17588,7 +17601,7 @@
         <v>464.82981280254529</v>
       </c>
     </row>
-    <row r="173" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A173" s="6" t="s">
         <v>175</v>
       </c>
@@ -17677,7 +17690,7 @@
         <v>16662.50358886016</v>
       </c>
     </row>
-    <row r="174" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A174" s="6" t="s">
         <v>46</v>
       </c>
@@ -17766,7 +17779,7 @@
         <v>841.93173999332305</v>
       </c>
     </row>
-    <row r="175" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A175" s="6" t="s">
         <v>223</v>
       </c>
@@ -17855,7 +17868,7 @@
         <v>1175.7176399303189</v>
       </c>
     </row>
-    <row r="176" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A176" s="6" t="s">
         <v>32</v>
       </c>
@@ -17944,7 +17957,7 @@
         <v>2363.787431674677</v>
       </c>
     </row>
-    <row r="177" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A177" s="6" t="s">
         <v>96</v>
       </c>
@@ -18033,7 +18046,7 @@
         <v>1592.421146155232</v>
       </c>
     </row>
-    <row r="178" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A178" s="6" t="s">
         <v>309</v>
       </c>
@@ -18122,7 +18135,7 @@
         <v>4435.8811785020507</v>
       </c>
     </row>
-    <row r="179" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A179" s="6" t="s">
         <v>284</v>
       </c>
@@ -18211,7 +18224,7 @@
         <v>196.6654698046213</v>
       </c>
     </row>
-    <row r="180" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A180" s="6" t="s">
         <v>292</v>
       </c>
@@ -18300,7 +18313,7 @@
         <v>992.27191272801929</v>
       </c>
     </row>
-    <row r="181" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A181" s="6" t="s">
         <v>101</v>
       </c>
@@ -18389,7 +18402,7 @@
         <v>78061.041432671904</v>
       </c>
     </row>
-    <row r="182" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A182" s="6" t="s">
         <v>67</v>
       </c>
@@ -18478,7 +18491,7 @@
         <v>304.38944941855232</v>
       </c>
     </row>
-    <row r="183" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A183" s="6" t="s">
         <v>156</v>
       </c>
@@ -18567,7 +18580,7 @@
         <v>10212.39455125783</v>
       </c>
     </row>
-    <row r="184" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A184" s="6" t="s">
         <v>283</v>
       </c>
@@ -18656,7 +18669,7 @@
         <v>18592.57998638527</v>
       </c>
     </row>
-    <row r="185" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A185" s="6" t="s">
         <v>119</v>
       </c>
@@ -18745,7 +18758,7 @@
         <v>1927.8276906159199</v>
       </c>
     </row>
-    <row r="186" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A186" s="6" t="s">
         <v>227</v>
       </c>
@@ -18834,7 +18847,7 @@
         <v>803.84135008458463</v>
       </c>
     </row>
-    <row r="187" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A187" s="6" t="s">
         <v>252</v>
       </c>
@@ -18923,7 +18936,7 @@
         <v>31846.275621980101</v>
       </c>
     </row>
-    <row r="188" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A188" s="6" t="s">
         <v>80</v>
       </c>
@@ -19012,7 +19025,7 @@
         <v>130.38723571853549</v>
       </c>
     </row>
-    <row r="189" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A189" s="6" t="s">
         <v>211</v>
       </c>
@@ -19101,7 +19114,7 @@
         <v>774.95830810213045</v>
       </c>
     </row>
-    <row r="190" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A190" s="6" t="s">
         <v>66</v>
       </c>
@@ -19190,7 +19203,7 @@
         <v>1916.4551652365981</v>
       </c>
     </row>
-    <row r="191" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A191" s="6" t="s">
         <v>254</v>
       </c>
@@ -19279,7 +19292,7 @@
         <v>133.93969906143721</v>
       </c>
     </row>
-    <row r="192" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A192" s="6" t="s">
         <v>59</v>
       </c>
@@ -19368,7 +19381,7 @@
         <v>17875.330193381182</v>
       </c>
     </row>
-    <row r="193" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A193" s="6" t="s">
         <v>208</v>
       </c>
@@ -19457,7 +19470,7 @@
         <v>105.6322642452615</v>
       </c>
     </row>
-    <row r="194" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A194" s="6" t="s">
         <v>286</v>
       </c>
@@ -19546,7 +19559,7 @@
         <v>2003.2134506127011</v>
       </c>
     </row>
-    <row r="195" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A195" s="6" t="s">
         <v>213</v>
       </c>
@@ -19635,7 +19648,7 @@
         <v>9194.2342876922303</v>
       </c>
     </row>
-    <row r="196" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A196" s="6" t="s">
         <v>89</v>
       </c>
@@ -19724,7 +19737,7 @@
         <v>1166.5912250119579</v>
       </c>
     </row>
-    <row r="197" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A197" s="6" t="s">
         <v>266</v>
       </c>
@@ -19813,7 +19826,7 @@
         <v>725.46796450111458</v>
       </c>
     </row>
-    <row r="198" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A198" s="6" t="s">
         <v>166</v>
       </c>
@@ -19902,7 +19915,7 @@
         <v>6839.0000649881149</v>
       </c>
     </row>
-    <row r="199" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A199" s="6" t="s">
         <v>48</v>
       </c>
@@ -19991,7 +20004,7 @@
         <v>2759.0978888817308</v>
       </c>
     </row>
-    <row r="200" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A200" s="6" t="s">
         <v>37</v>
       </c>
@@ -20080,7 +20093,7 @@
         <v>3953.5797555877152</v>
       </c>
     </row>
-    <row r="201" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A201" s="6" t="s">
         <v>265</v>
       </c>
@@ -20169,7 +20182,7 @@
         <v>2137.0003167564141</v>
       </c>
     </row>
-    <row r="202" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A202" s="6" t="s">
         <v>74</v>
       </c>
@@ -20258,7 +20271,7 @@
         <v>2098.8400342582909</v>
       </c>
     </row>
-    <row r="203" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A203" s="6" t="s">
         <v>118</v>
       </c>
@@ -20347,7 +20360,7 @@
         <v>1387.4507104059001</v>
       </c>
     </row>
-    <row r="204" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A204" s="6" t="s">
         <v>264</v>
       </c>
@@ -20436,7 +20449,7 @@
         <v>293.92998520785699</v>
       </c>
     </row>
-    <row r="205" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A205" s="6" t="s">
         <v>69</v>
       </c>
@@ -20525,7 +20538,7 @@
         <v>440.99724215402279</v>
       </c>
     </row>
-    <row r="206" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A206" s="6" t="s">
         <v>158</v>
       </c>
@@ -20614,7 +20627,7 @@
         <v>8645.8218837224158</v>
       </c>
     </row>
-    <row r="207" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A207" s="6" t="s">
         <v>299</v>
       </c>
@@ -20703,7 +20716,7 @@
         <v>304.67372091044041</v>
       </c>
     </row>
-    <row r="208" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A208" s="6" t="s">
         <v>310</v>
       </c>
@@ -20792,7 +20805,7 @@
         <v>11147.9293699187</v>
       </c>
     </row>
-    <row r="209" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A209" s="6" t="s">
         <v>84</v>
       </c>
@@ -20881,7 +20894,7 @@
         <v>1448.959169677506</v>
       </c>
     </row>
-    <row r="210" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A210" s="6" t="s">
         <v>205</v>
       </c>
@@ -20970,7 +20983,7 @@
         <v>1639.5951292102211</v>
       </c>
     </row>
-    <row r="211" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A211" s="6" t="s">
         <v>150</v>
       </c>
@@ -21059,7 +21072,7 @@
         <v>5909.8090219812893</v>
       </c>
     </row>
-    <row r="212" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A212" s="6" t="s">
         <v>113</v>
       </c>
@@ -21148,7 +21161,7 @@
         <v>4694.0170340540772</v>
       </c>
     </row>
-    <row r="213" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A213" s="6" t="s">
         <v>179</v>
       </c>
@@ -21237,7 +21250,7 @@
         <v>289.87813572109178</v>
       </c>
     </row>
-    <row r="214" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A214" s="6" t="s">
         <v>64</v>
       </c>
@@ -21326,7 +21339,7 @@
         <v>1574.1558031859131</v>
       </c>
     </row>
-    <row r="215" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A215" s="6" t="s">
         <v>218</v>
       </c>
@@ -21415,7 +21428,7 @@
         <v>1084.603614369146</v>
       </c>
     </row>
-    <row r="216" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A216" s="6" t="s">
         <v>306</v>
       </c>
@@ -21504,7 +21517,7 @@
         <v>485.64340862300929</v>
       </c>
     </row>
-    <row r="217" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A217" s="6" t="s">
         <v>275</v>
       </c>
@@ -21593,7 +21606,7 @@
         <v>16799.039176968839</v>
       </c>
     </row>
-    <row r="218" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A218" s="6" t="s">
         <v>226</v>
       </c>
@@ -21682,7 +21695,7 @@
         <v>1853.6733023580259</v>
       </c>
     </row>
-    <row r="219" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A219" s="6" t="s">
         <v>29</v>
       </c>
@@ -21771,7 +21784,7 @@
         <v>275.1640684641261</v>
       </c>
     </row>
-    <row r="220" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A220" s="6" t="s">
         <v>228</v>
       </c>
@@ -21860,7 +21873,7 @@
         <v>10742.772159651069</v>
       </c>
     </row>
-    <row r="221" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A221" s="6" t="s">
         <v>187</v>
       </c>
@@ -21949,7 +21962,7 @@
         <v>600.04974486681795</v>
       </c>
     </row>
-    <row r="222" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A222" s="6" t="s">
         <v>239</v>
       </c>
@@ -22038,7 +22051,7 @@
         <v>1254.2912218268091</v>
       </c>
     </row>
-    <row r="223" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A223" s="6" t="s">
         <v>318</v>
       </c>
@@ -22127,7 +22140,7 @@
         <v>409.82361829267359</v>
       </c>
     </row>
-    <row r="224" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A224" s="6" t="s">
         <v>192</v>
       </c>
@@ -22216,7 +22229,7 @@
         <v>3947.2023476451241</v>
       </c>
     </row>
-    <row r="225" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A225" s="6" t="s">
         <v>167</v>
       </c>
@@ -22305,7 +22318,7 @@
         <v>922.93584500130885</v>
       </c>
     </row>
-    <row r="226" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A226" s="6" t="s">
         <v>178</v>
       </c>
@@ -22394,7 +22407,7 @@
         <v>2011.0409243062311</v>
       </c>
     </row>
-    <row r="227" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A227" s="6" t="s">
         <v>58</v>
       </c>
@@ -22483,7 +22496,7 @@
         <v>202.80520913961911</v>
       </c>
     </row>
-    <row r="228" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A228" s="6" t="s">
         <v>91</v>
       </c>
@@ -22572,7 +22585,7 @@
         <v>4316.6373894190438</v>
       </c>
     </row>
-    <row r="229" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A229" s="6" t="s">
         <v>169</v>
       </c>
@@ -22661,7 +22674,7 @@
         <v>6201.2651298582814</v>
       </c>
     </row>
-    <row r="230" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A230" s="6" t="s">
         <v>199</v>
       </c>
@@ -22750,7 +22763,7 @@
         <v>16846.408303464781</v>
       </c>
     </row>
-    <row r="231" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A231" s="6" t="s">
         <v>147</v>
       </c>
@@ -22839,7 +22852,7 @@
         <v>5308.2004366502642</v>
       </c>
     </row>
-    <row r="232" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A232" s="6" t="s">
         <v>237</v>
       </c>
@@ -22928,7 +22941,7 @@
         <v>3730.421632423871</v>
       </c>
     </row>
-    <row r="233" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A233" s="6" t="s">
         <v>305</v>
       </c>
@@ -23017,7 +23030,7 @@
         <v>105.14457784372971</v>
       </c>
     </row>
-    <row r="234" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A234" s="6" t="s">
         <v>287</v>
       </c>
@@ -23106,7 +23119,7 @@
         <v>1099.6904442161169</v>
       </c>
     </row>
-    <row r="235" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A235" s="6" t="s">
         <v>300</v>
       </c>
@@ -23195,7 +23208,7 @@
         <v>16929.391399416909</v>
       </c>
     </row>
-    <row r="236" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A236" s="6" t="s">
         <v>209</v>
       </c>
@@ -23284,7 +23297,7 @@
         <v>1260.8443843370021</v>
       </c>
     </row>
-    <row r="237" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A237" s="6" t="s">
         <v>184</v>
       </c>
@@ -23373,7 +23386,7 @@
         <v>822.90292981670018</v>
       </c>
     </row>
-    <row r="238" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A238" s="6" t="s">
         <v>280</v>
       </c>
@@ -23462,7 +23475,7 @@
         <v>109.4238689479931</v>
       </c>
     </row>
-    <row r="239" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A239" s="6" t="s">
         <v>315</v>
       </c>
@@ -23551,7 +23564,7 @@
         <v>225.62187112018901</v>
       </c>
     </row>
-    <row r="240" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A240" s="6" t="s">
         <v>82</v>
       </c>
@@ -23640,7 +23653,7 @@
         <v>3015.7722653474352</v>
       </c>
     </row>
-    <row r="241" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A241" s="6" t="s">
         <v>71</v>
       </c>
@@ -23729,7 +23742,7 @@
         <v>3795.424348114931</v>
       </c>
     </row>
-    <row r="242" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A242" s="6" t="s">
         <v>313</v>
       </c>
@@ -23818,7 +23831,7 @@
         <v>1228.014650638617</v>
       </c>
     </row>
-    <row r="243" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A243" s="6" t="s">
         <v>214</v>
       </c>
@@ -23907,7 +23920,7 @@
         <v>5160.3637710332841</v>
       </c>
     </row>
-    <row r="244" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A244" s="6" t="s">
         <v>117</v>
       </c>
@@ -23996,7 +24009,7 @@
         <v>3914.6835649030781</v>
       </c>
     </row>
-    <row r="245" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A245" s="6" t="s">
         <v>161</v>
       </c>
@@ -24085,7 +24098,7 @@
         <v>98.760233049349864</v>
       </c>
     </row>
-    <row r="246" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A246" s="6" t="s">
         <v>277</v>
       </c>
@@ -24174,7 +24187,7 @@
         <v>71.03430694635351</v>
       </c>
     </row>
-    <row r="247" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A247" s="6" t="s">
         <v>163</v>
       </c>
@@ -24263,7 +24276,7 @@
         <v>1627.3387793628781</v>
       </c>
     </row>
-    <row r="248" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A248" s="6" t="s">
         <v>132</v>
       </c>
@@ -24352,7 +24365,7 @@
         <v>2548.514835930217</v>
       </c>
     </row>
-    <row r="249" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A249" s="6" t="s">
         <v>317</v>
       </c>
@@ -24441,7 +24454,7 @@
         <v>816.38163648882528</v>
       </c>
     </row>
-    <row r="250" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A250" s="6" t="s">
         <v>181</v>
       </c>
@@ -24530,7 +24543,7 @@
         <v>124.75322351091491</v>
       </c>
     </row>
-    <row r="251" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A251" s="6" t="s">
         <v>327</v>
       </c>
@@ -24619,7 +24632,7 @@
         <v>784.54740897922704</v>
       </c>
     </row>
-    <row r="252" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A252" s="6" t="s">
         <v>270</v>
       </c>
@@ -24708,7 +24721,7 @@
         <v>2905.58591797701</v>
       </c>
     </row>
-    <row r="253" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A253" s="6" t="s">
         <v>35</v>
       </c>
@@ -24797,7 +24810,7 @@
         <v>115.4957939595962</v>
       </c>
     </row>
-    <row r="254" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A254" s="6" t="s">
         <v>244</v>
       </c>
@@ -24886,7 +24899,7 @@
         <v>86.956970697429725</v>
       </c>
     </row>
-    <row r="255" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A255" s="6" t="s">
         <v>259</v>
       </c>
@@ -24975,7 +24988,7 @@
         <v>253.62056939813999</v>
       </c>
     </row>
-    <row r="256" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A256" s="6" t="s">
         <v>170</v>
       </c>
@@ -25064,7 +25077,7 @@
         <v>2506.736708247548</v>
       </c>
     </row>
-    <row r="257" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A257" s="6" t="s">
         <v>94</v>
       </c>
@@ -25153,7 +25166,7 @@
         <v>49.972401514510921</v>
       </c>
     </row>
-    <row r="258" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A258" s="6" t="s">
         <v>126</v>
       </c>
@@ -25242,7 +25255,7 @@
         <v>13810.092508340909</v>
       </c>
     </row>
-    <row r="259" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A259" s="6" t="s">
         <v>116</v>
       </c>
@@ -25331,7 +25344,7 @@
         <v>3395.6253284287968</v>
       </c>
     </row>
-    <row r="260" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A260" s="6" t="s">
         <v>222</v>
       </c>
@@ -25420,7 +25433,7 @@
         <v>4454.5447267720183</v>
       </c>
     </row>
-    <row r="261" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A261" s="6" t="s">
         <v>247</v>
       </c>
@@ -25509,7 +25522,7 @@
         <v>202.49156308845329</v>
       </c>
     </row>
-    <row r="262" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A262" s="6" t="s">
         <v>151</v>
       </c>
@@ -25598,7 +25611,7 @@
         <v>3360.6836092108829</v>
       </c>
     </row>
-    <row r="263" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A263" s="6" t="s">
         <v>51</v>
       </c>
@@ -25687,7 +25700,7 @@
         <v>393.32205851475322</v>
       </c>
     </row>
-    <row r="264" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A264" s="6" t="s">
         <v>47</v>
       </c>
@@ -25776,7 +25789,7 @@
         <v>181.17564068803031</v>
       </c>
     </row>
-    <row r="265" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A265" s="6" t="s">
         <v>153</v>
       </c>
@@ -25865,7 +25878,7 @@
         <v>1468.3798120977269</v>
       </c>
     </row>
-    <row r="266" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A266" s="6" t="s">
         <v>120</v>
       </c>
@@ -25954,7 +25967,7 @@
         <v>1065.626319628393</v>
       </c>
     </row>
-    <row r="267" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A267" s="6" t="s">
         <v>245</v>
       </c>
@@ -26043,7 +26056,7 @@
         <v>8413.5286161731201</v>
       </c>
     </row>
-    <row r="268" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A268" s="6" t="s">
         <v>204</v>
       </c>
@@ -26132,7 +26145,7 @@
         <v>55.817740292889177</v>
       </c>
     </row>
-    <row r="269" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A269" s="6" t="s">
         <v>207</v>
       </c>
@@ -26221,7 +26234,7 @@
         <v>5875.1065966109154</v>
       </c>
     </row>
-    <row r="270" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A270" s="6" t="s">
         <v>123</v>
       </c>
@@ -26310,7 +26323,7 @@
         <v>214.68720365806661</v>
       </c>
     </row>
-    <row r="271" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A271" s="6" t="s">
         <v>40</v>
       </c>
@@ -26399,7 +26412,7 @@
         <v>559.75264217117024</v>
       </c>
     </row>
-    <row r="272" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A272" s="6" t="s">
         <v>216</v>
       </c>
@@ -26488,7 +26501,7 @@
         <v>682.31412966878099</v>
       </c>
     </row>
-    <row r="273" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A273" s="6" t="s">
         <v>55</v>
       </c>
@@ -26577,7 +26590,7 @@
         <v>317.92260071361039</v>
       </c>
     </row>
-    <row r="274" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A274" s="6" t="s">
         <v>141</v>
       </c>
@@ -26666,7 +26679,7 @@
         <v>903.46260062874092</v>
       </c>
     </row>
-    <row r="275" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A275" s="6" t="s">
         <v>294</v>
       </c>
@@ -26755,7 +26768,7 @@
         <v>2083.0318721700619</v>
       </c>
     </row>
-    <row r="276" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A276" s="6" t="s">
         <v>225</v>
       </c>
@@ -26844,7 +26857,7 @@
         <v>649.05815393408238</v>
       </c>
     </row>
-    <row r="277" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A277" s="6" t="s">
         <v>224</v>
       </c>
@@ -26933,7 +26946,7 @@
         <v>4362.2190222216077</v>
       </c>
     </row>
-    <row r="278" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A278" s="6" t="s">
         <v>323</v>
       </c>
@@ -27022,7 +27035,7 @@
         <v>24.134686550337602</v>
       </c>
     </row>
-    <row r="279" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A279" s="6" t="s">
         <v>229</v>
       </c>
@@ -27111,7 +27124,7 @@
         <v>2615.7917603230112</v>
       </c>
     </row>
-    <row r="280" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A280" s="6" t="s">
         <v>36</v>
       </c>
@@ -27200,7 +27213,7 @@
         <v>5667.7653538050718</v>
       </c>
     </row>
-    <row r="281" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A281" s="6" t="s">
         <v>269</v>
       </c>
@@ -27289,7 +27302,7 @@
         <v>1789.4153802172671</v>
       </c>
     </row>
-    <row r="282" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A282" s="6" t="s">
         <v>233</v>
       </c>
@@ -27378,7 +27391,7 @@
         <v>572.06524162541291</v>
       </c>
     </row>
-    <row r="283" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A283" s="6" t="s">
         <v>289</v>
       </c>
@@ -27467,7 +27480,7 @@
         <v>2910.616954778272</v>
       </c>
     </row>
-    <row r="284" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A284" s="6" t="s">
         <v>221</v>
       </c>
@@ -27556,7 +27569,7 @@
         <v>153.03015192801629</v>
       </c>
     </row>
-    <row r="285" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A285" s="6" t="s">
         <v>103</v>
       </c>
@@ -27645,7 +27658,7 @@
         <v>9189.5906781203958</v>
       </c>
     </row>
-    <row r="286" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A286" s="6" t="s">
         <v>219</v>
       </c>
@@ -27734,7 +27747,7 @@
         <v>184.59698833530609</v>
       </c>
     </row>
-    <row r="287" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A287" s="6" t="s">
         <v>149</v>
       </c>
@@ -27823,7 +27836,7 @@
         <v>39.968107242333289</v>
       </c>
     </row>
-    <row r="288" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A288" s="6" t="s">
         <v>311</v>
       </c>
@@ -27912,7 +27925,7 @@
         <v>121.94607156891639</v>
       </c>
     </row>
-    <row r="289" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A289" s="6" t="s">
         <v>109</v>
       </c>
@@ -28001,7 +28014,7 @@
         <v>308.10396851627428</v>
       </c>
     </row>
-    <row r="290" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A290" s="6" t="s">
         <v>288</v>
       </c>
@@ -28090,7 +28103,7 @@
         <v>1236.7176229236979</v>
       </c>
     </row>
-    <row r="291" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A291" s="6" t="s">
         <v>180</v>
       </c>
@@ -28179,7 +28192,7 @@
         <v>382.91491864102619</v>
       </c>
     </row>
-    <row r="292" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A292" s="6" t="s">
         <v>70</v>
       </c>
@@ -28268,7 +28281,7 @@
         <v>2832.3659673659649</v>
       </c>
     </row>
-    <row r="293" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A293" s="6" t="s">
         <v>297</v>
       </c>
@@ -28357,7 +28370,7 @@
         <v>772.51809543960883</v>
       </c>
     </row>
-    <row r="294" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A294" s="6" t="s">
         <v>121</v>
       </c>
@@ -28446,7 +28459,7 @@
         <v>726.96452692989237</v>
       </c>
     </row>
-    <row r="295" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A295" s="6" t="s">
         <v>196</v>
       </c>
@@ -28535,7 +28548,7 @@
         <v>547.62635097640248</v>
       </c>
     </row>
-    <row r="296" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A296" s="6" t="s">
         <v>273</v>
       </c>
@@ -28624,7 +28637,7 @@
         <v>31.447743319984891</v>
       </c>
     </row>
-    <row r="297" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A297" s="6" t="s">
         <v>234</v>
       </c>
@@ -28713,7 +28726,7 @@
         <v>117.1211338203951</v>
       </c>
     </row>
-    <row r="298" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A298" s="6" t="s">
         <v>143</v>
       </c>
@@ -28802,7 +28815,7 @@
         <v>1655.048897801415</v>
       </c>
     </row>
-    <row r="299" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A299" s="6" t="s">
         <v>203</v>
       </c>
@@ -28891,7 +28904,7 @@
         <v>222.65500286135949</v>
       </c>
     </row>
-    <row r="300" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A300" s="6" t="s">
         <v>320</v>
       </c>
@@ -28980,7 +28993,7 @@
         <v>159.1748915662651</v>
       </c>
     </row>
-    <row r="301" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A301" s="6" t="s">
         <v>328</v>
       </c>
